--- a/rExtra_infravermelho/dados/planilha_tcrt5000.xlsx
+++ b/rExtra_infravermelho/dados/planilha_tcrt5000.xlsx
@@ -749,7 +749,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>O ajuste usado no Arduino é o de 20–100 mm (linhas 2–10), como na planilha da equipe. 110 e 120 mm ficaram fora e servem de validação; 200 mm está dentro do fundo (sinal 2, menores leituras com o alvo afastado: 3–5).</t>
+          <t>O ajuste usado no Arduino é o de 20–100 mm (linhas 2–10), como na planilha da equipe. 110 e 120 mm ficaram fora e servem de validação; 200 mm está dentro do fundo (sinal 2; com o alvo afastado, o fundo ficou entre 4 e 5 contagens).</t>
         </is>
       </c>
     </row>
